--- a/output/pdf_financials_xlsx/REDC.xlsx
+++ b/output/pdf_financials_xlsx/REDC.xlsx
@@ -1908,7 +1908,7 @@
         <v>-0.011969</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.004886</v>
       </c>
     </row>
     <row r="92">
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.278053</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.564657</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.681324</v>
       </c>
     </row>
     <row r="93">
@@ -3140,7 +3140,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.278053</v>
       </c>
@@ -3163,7 +3167,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/REDC.xlsx
+++ b/output/pdf_financials_xlsx/REDC.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.245121</v>
+        <v>0.477558</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.331543</v>
+        <v>0.823108</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.306047</v>
+        <v>0.59202</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.245121</v>
+        <v>-0.477558</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.331543</v>
+        <v>-0.823108</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.306047</v>
+        <v>-0.59202</v>
       </c>
     </row>
     <row r="12">
@@ -615,7 +615,7 @@
         <v>0.047148</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.038537</v>
       </c>
     </row>
     <row r="13">
@@ -869,7 +869,7 @@
         <v>-0.664011</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.038812</v>
+        <v>-1.077349</v>
       </c>
     </row>
     <row r="28">
@@ -901,7 +901,7 @@
         <v>-0.663305</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.037907</v>
+        <v>-1.076444</v>
       </c>
     </row>
     <row r="30">
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.96862</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.6880309999999999</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.96862</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.6880309999999999</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.009311</v>
+        <v>0.040691</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.056133</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>-0.477558</v>
+        <v>0.477558</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.823108</v>
+        <v>0.823108</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.59202</v>
+        <v>0.59202</v>
       </c>
     </row>
     <row r="74">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">

--- a/output/pdf_financials_xlsx/REDC.xlsx
+++ b/output/pdf_financials_xlsx/REDC.xlsx
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001852</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0015</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001852</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0015</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.534834</v>
+        <v>-0.536686</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.620103</v>
+        <v>-0.621603</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.562581</v>
@@ -3552,7 +3552,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -3765,7 +3769,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>-0.001852</v>
       </c>
@@ -3825,7 +3833,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>2.440457</v>
       </c>
